--- a/grupos/4ALCM - Estadisticos 20232.xlsx
+++ b/grupos/4ALCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -224,6 +224,9 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Hernández Cides Ricardo</t>
+  </si>
+  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -233,9 +236,6 @@
     <t>Hernández Castro Enrique</t>
   </si>
   <si>
-    <t>Hernández Cides Ricardo</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -254,9 +254,6 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>OLMOS</t>
   </si>
   <si>
@@ -266,9 +263,6 @@
     <t>PRADO</t>
   </si>
   <si>
-    <t>LUGO</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -276,9 +270,6 @@
   </si>
   <si>
     <t>ANETTE</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
   </si>
   <si>
     <t>AHILY</t>
@@ -811,25 +802,25 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -853,7 +844,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -900,25 +891,25 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -989,25 +980,25 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1031,25 +1022,25 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z6">
         <v>10</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB6">
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1078,25 +1069,25 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1126,10 +1117,10 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>9</v>
@@ -1167,25 +1158,25 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1209,25 +1200,25 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
       </c>
       <c r="Z8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB8">
         <v>10</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1256,25 +1247,25 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1304,7 +1295,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z9">
         <v>7</v>
@@ -1345,25 +1336,25 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1434,25 +1425,25 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1482,19 +1473,19 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>10</v>
       </c>
       <c r="AA11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB11">
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1523,25 +1514,25 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1565,16 +1556,16 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>10</v>
@@ -1612,25 +1603,25 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1654,16 +1645,16 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA13">
         <v>10</v>
@@ -1701,25 +1692,25 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1749,19 +1740,19 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB14">
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1790,25 +1781,25 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1838,19 +1829,19 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z15">
         <v>8</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB15">
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1879,25 +1870,25 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1921,13 +1912,13 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z16">
         <v>7</v>
@@ -1936,7 +1927,7 @@
         <v>9</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC16">
         <v>9</v>
@@ -1968,25 +1959,25 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2010,25 +2001,25 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB17">
         <v>10</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2057,25 +2048,25 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2105,10 +2096,10 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -2146,25 +2137,25 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2188,7 +2179,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2200,13 +2191,13 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB19">
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2235,25 +2226,25 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2277,16 +2268,16 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA20">
         <v>10</v>
@@ -2324,25 +2315,25 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2366,7 +2357,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2378,13 +2369,13 @@
         <v>6</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB21">
         <v>10</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2413,25 +2404,25 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2455,25 +2446,25 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB22">
         <v>9</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2502,25 +2493,25 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2544,25 +2535,25 @@
         <v>-1</v>
       </c>
       <c r="W23">
+        <v>9</v>
+      </c>
+      <c r="X23">
         <v>7</v>
       </c>
-      <c r="X23">
-        <v>8</v>
-      </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z23">
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2591,25 +2582,25 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2639,19 +2630,19 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z24">
         <v>10</v>
       </c>
       <c r="AA24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB24">
         <v>10</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2680,25 +2671,25 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2769,25 +2760,25 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2811,25 +2802,25 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB26">
         <v>10</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2858,25 +2849,25 @@
         <v>7</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2900,25 +2891,25 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z27">
         <v>6</v>
       </c>
       <c r="AA27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB27">
         <v>9</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -2947,25 +2938,25 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3036,25 +3027,25 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3078,25 +3069,25 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z29">
         <v>5</v>
       </c>
       <c r="AA29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3125,25 +3116,25 @@
         <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3173,19 +3164,19 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3214,25 +3205,25 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3262,10 +3253,10 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA31">
         <v>10</v>
@@ -3303,25 +3294,25 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3351,7 +3342,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z32">
         <v>9</v>
@@ -3392,25 +3383,25 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3434,16 +3425,16 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA33">
         <v>10</v>
@@ -3481,25 +3472,25 @@
         <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3529,19 +3520,19 @@
         <v>10</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB34">
         <v>10</v>
       </c>
       <c r="AC34">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -3570,25 +3561,25 @@
         <v>9</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3618,19 +3609,19 @@
         <v>9</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z35">
         <v>7</v>
       </c>
       <c r="AA35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB35">
         <v>10</v>
       </c>
       <c r="AC35">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3659,25 +3650,25 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3748,25 +3739,25 @@
         <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3790,25 +3781,25 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z37">
         <v>5</v>
       </c>
       <c r="AA37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC37">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -3837,25 +3828,25 @@
         <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3926,25 +3917,25 @@
         <v>9</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -3968,16 +3959,16 @@
         <v>-1</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X39">
         <v>9</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA39">
         <v>9</v>
@@ -4015,25 +4006,25 @@
         <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -4057,16 +4048,16 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X40">
         <v>9</v>
       </c>
       <c r="Y40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA40">
         <v>10</v>
@@ -4104,25 +4095,25 @@
         <v>10</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4193,25 +4184,25 @@
         <v>8</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -4235,25 +4226,25 @@
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X42">
         <v>10</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z42">
         <v>7</v>
       </c>
       <c r="AA42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB42">
         <v>10</v>
       </c>
       <c r="AC42">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:29">
@@ -4282,25 +4273,25 @@
         <v>5</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P43">
         <v>-1</v>
@@ -4371,25 +4362,25 @@
         <v>9</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P44">
         <v>-1</v>
@@ -4413,16 +4404,16 @@
         <v>-1</v>
       </c>
       <c r="W44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X44">
         <v>9</v>
       </c>
       <c r="Y44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z44">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA44">
         <v>9</v>
@@ -4460,25 +4451,25 @@
         <v>10</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P45">
         <v>-1</v>
@@ -4819,13 +4810,13 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -4840,13 +4831,13 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="U6">
         <v>100</v>
       </c>
       <c r="V6">
-        <v>90</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4887,13 +4878,13 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N7">
-        <v>91.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="O7">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -4908,13 +4899,13 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U7">
-        <v>91.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="V7">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -5023,13 +5014,13 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -5044,13 +5035,13 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U9">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="V9">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -5499,13 +5490,13 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N16">
-        <v>91.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -5520,13 +5511,13 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U16">
-        <v>91.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V16">
-        <v>100</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5635,13 +5626,13 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="N18">
-        <v>91.40000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O18">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -5656,13 +5647,13 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="U18">
-        <v>91.40000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="V18">
-        <v>90</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5703,13 +5694,13 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -5724,13 +5715,13 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="U19">
         <v>100</v>
       </c>
       <c r="V19">
-        <v>93.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5774,7 +5765,7 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>94.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -5795,7 +5786,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>94.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -5907,13 +5898,13 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N22">
-        <v>94.3</v>
+        <v>92.2</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -5928,13 +5919,13 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U22">
-        <v>94.3</v>
+        <v>92.2</v>
       </c>
       <c r="V22">
-        <v>100</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5972,16 +5963,16 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="M23">
-        <v>80</v>
+        <v>77.3</v>
       </c>
       <c r="N23">
-        <v>85.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O23">
-        <v>80</v>
+        <v>84.8</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -5993,16 +5984,16 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="T23">
-        <v>80</v>
+        <v>77.3</v>
       </c>
       <c r="U23">
-        <v>85.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V23">
-        <v>80</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -6043,13 +6034,13 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="N24">
         <v>100</v>
       </c>
       <c r="O24">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -6064,13 +6055,13 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="U24">
         <v>100</v>
       </c>
       <c r="V24">
-        <v>93.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -6111,13 +6102,13 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="N25">
         <v>100</v>
       </c>
       <c r="O25">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -6132,13 +6123,13 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="U25">
         <v>100</v>
       </c>
       <c r="V25">
-        <v>93.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -6179,13 +6170,13 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="N26">
         <v>100</v>
       </c>
       <c r="O26">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -6200,13 +6191,13 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="U26">
         <v>100</v>
       </c>
       <c r="V26">
-        <v>93.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6247,13 +6238,13 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N27">
-        <v>94.3</v>
+        <v>94.8</v>
       </c>
       <c r="O27">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -6268,13 +6259,13 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U27">
-        <v>94.3</v>
+        <v>94.8</v>
       </c>
       <c r="V27">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6380,16 +6371,16 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="M29">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="N29">
-        <v>94.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O29">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -6401,16 +6392,16 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="T29">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="U29">
-        <v>94.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V29">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6448,16 +6439,16 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="M30">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="N30">
-        <v>94.3</v>
+        <v>92.2</v>
       </c>
       <c r="O30">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -6469,16 +6460,16 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="T30">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="U30">
-        <v>94.3</v>
+        <v>92.2</v>
       </c>
       <c r="V30">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6519,13 +6510,13 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="N31">
         <v>100</v>
       </c>
       <c r="O31">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -6540,13 +6531,13 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="U31">
         <v>100</v>
       </c>
       <c r="V31">
-        <v>93.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6587,13 +6578,13 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="N32">
         <v>100</v>
       </c>
       <c r="O32">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -6608,13 +6599,13 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="U32">
         <v>100</v>
       </c>
       <c r="V32">
-        <v>86.7</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6723,13 +6714,13 @@
         <v>100</v>
       </c>
       <c r="M34">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="N34">
         <v>100</v>
       </c>
       <c r="O34">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -6744,13 +6735,13 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="U34">
         <v>100</v>
       </c>
       <c r="V34">
-        <v>93.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6791,13 +6782,13 @@
         <v>100</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N35">
-        <v>94.3</v>
+        <v>94.8</v>
       </c>
       <c r="O35">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="P35">
         <v>100</v>
@@ -6812,13 +6803,13 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U35">
-        <v>94.3</v>
+        <v>94.8</v>
       </c>
       <c r="V35">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6915,46 +6906,46 @@
         <v>90</v>
       </c>
       <c r="I37">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J37">
         <v>100</v>
       </c>
       <c r="K37">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="L37">
-        <v>100</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="M37">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N37">
-        <v>94.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O37">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P37">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q37">
         <v>100</v>
       </c>
       <c r="R37">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="T37">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U37">
-        <v>94.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V37">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -7063,13 +7054,13 @@
         <v>100</v>
       </c>
       <c r="M39">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N39">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -7084,13 +7075,13 @@
         <v>100</v>
       </c>
       <c r="T39">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U39">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="V39">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -7131,13 +7122,13 @@
         <v>100</v>
       </c>
       <c r="M40">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N40">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O40">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P40">
         <v>100</v>
@@ -7152,13 +7143,13 @@
         <v>100</v>
       </c>
       <c r="T40">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U40">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="V40">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -7267,10 +7258,10 @@
         <v>100</v>
       </c>
       <c r="M42">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N42">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O42">
         <v>100</v>
@@ -7288,10 +7279,10 @@
         <v>100</v>
       </c>
       <c r="T42">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U42">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="V42">
         <v>100</v>
@@ -7335,13 +7326,13 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>30</v>
+        <v>13.6</v>
       </c>
       <c r="N43">
-        <v>28.6</v>
+        <v>13</v>
       </c>
       <c r="O43">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -7356,13 +7347,13 @@
         <v>0</v>
       </c>
       <c r="T43">
-        <v>30</v>
+        <v>13.6</v>
       </c>
       <c r="U43">
-        <v>28.6</v>
+        <v>13</v>
       </c>
       <c r="V43">
-        <v>20</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -7403,10 +7394,10 @@
         <v>100</v>
       </c>
       <c r="M44">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N44">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O44">
         <v>100</v>
@@ -7424,10 +7415,10 @@
         <v>100</v>
       </c>
       <c r="T44">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U44">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="V44">
         <v>100</v>
@@ -7587,7 +7578,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
@@ -7596,19 +7587,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="G3" s="2">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7619,28 +7610,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4">
         <v>42</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="G4" s="2">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7651,10 +7642,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5">
         <v>42</v>
@@ -7672,7 +7663,7 @@
         <v>2.4</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7683,10 +7674,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <v>42</v>
@@ -7715,10 +7706,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7">
         <v>42</v>
@@ -7736,7 +7727,7 @@
         <v>2.4</v>
       </c>
       <c r="H7">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7747,10 +7738,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8">
         <v>42</v>
@@ -7768,7 +7759,7 @@
         <v>2.4</v>
       </c>
       <c r="H8">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7818,7 +7809,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7856,10 +7847,10 @@
         <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -7873,16 +7864,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920100</v>
+        <v>22330051920107</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7896,16 +7887,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920107</v>
+        <v>22330051920116</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -7914,29 +7905,6 @@
         <v>67</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920116</v>
-      </c>
-      <c r="B5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ALCM - Estadisticos 20232.xlsx
+++ b/grupos/4ALCM - Estadisticos 20232.xlsx
@@ -224,18 +224,18 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Faltante Faltante Faltante</t>
+  </si>
+  <si>
+    <t>Hernández Castro Enrique</t>
+  </si>
+  <si>
     <t>Hernández Cides Ricardo</t>
   </si>
   <si>
-    <t>Faltante Faltante Faltante</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Hernández Castro Enrique</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -251,7 +251,7 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>OLMOS</t>
@@ -260,7 +260,7 @@
     <t>ROJAS</t>
   </si>
   <si>
-    <t>PRADO</t>
+    <t>LUGO</t>
   </si>
   <si>
     <t>BAUTISTA</t>
@@ -269,7 +269,7 @@
     <t>SOTO</t>
   </si>
   <si>
-    <t>ANETTE</t>
+    <t>ZAYRA</t>
   </si>
   <si>
     <t>AHILY</t>
@@ -823,25 +823,25 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -912,31 +912,31 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>10</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -1001,25 +1001,25 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1090,25 +1090,25 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1123,7 +1123,7 @@
         <v>8</v>
       </c>
       <c r="AA7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB7">
         <v>9</v>
@@ -1179,25 +1179,25 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1268,25 +1268,25 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1301,13 +1301,13 @@
         <v>7</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1357,25 +1357,25 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1446,25 +1446,25 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1535,25 +1535,25 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1624,25 +1624,25 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1713,25 +1713,25 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1802,25 +1802,25 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>10</v>
@@ -1891,25 +1891,25 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1980,25 +1980,25 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2069,25 +2069,25 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>10</v>
@@ -2158,25 +2158,25 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2188,7 +2188,7 @@
         <v>9</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>9</v>
@@ -2247,25 +2247,25 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2336,37 +2336,37 @@
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>8</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>9</v>
       </c>
       <c r="Z21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>9</v>
@@ -2425,25 +2425,25 @@
         <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2458,13 +2458,13 @@
         <v>7</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2514,31 +2514,31 @@
         <v>4</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>9</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2547,13 +2547,13 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB23">
         <v>6</v>
       </c>
       <c r="AC23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2603,31 +2603,31 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>10</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2692,25 +2692,25 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2781,25 +2781,25 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2811,7 +2811,7 @@
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA26">
         <v>10</v>
@@ -2870,43 +2870,43 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>9</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>9</v>
       </c>
       <c r="Z27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>8</v>
       </c>
       <c r="AB27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -2959,31 +2959,31 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>10</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -3048,31 +3048,31 @@
         <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>9</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -3081,13 +3081,13 @@
         <v>5</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3137,28 +3137,28 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3167,7 +3167,7 @@
         <v>10</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA30">
         <v>8</v>
@@ -3226,25 +3226,25 @@
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3315,25 +3315,25 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3345,7 +3345,7 @@
         <v>10</v>
       </c>
       <c r="Z32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA32">
         <v>10</v>
@@ -3404,25 +3404,25 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>9</v>
@@ -3493,25 +3493,25 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3582,25 +3582,25 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>10</v>
@@ -3615,13 +3615,13 @@
         <v>7</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB35">
         <v>10</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3671,25 +3671,25 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W36">
         <v>10</v>
@@ -3760,43 +3760,43 @@
         <v>7</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X37">
+        <v>5</v>
+      </c>
+      <c r="Y37">
+        <v>9</v>
+      </c>
+      <c r="Z37">
         <v>6</v>
       </c>
-      <c r="Y37">
-        <v>8</v>
-      </c>
-      <c r="Z37">
-        <v>5</v>
-      </c>
       <c r="AA37">
         <v>8</v>
       </c>
       <c r="AB37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC37">
         <v>8</v>
@@ -3849,25 +3849,25 @@
         <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3938,25 +3938,25 @@
         <v>9</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W39">
         <v>10</v>
@@ -4027,25 +4027,25 @@
         <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W40">
         <v>10</v>
@@ -4116,25 +4116,25 @@
         <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W41">
         <v>10</v>
@@ -4205,25 +4205,25 @@
         <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W42">
         <v>10</v>
@@ -4235,7 +4235,7 @@
         <v>9</v>
       </c>
       <c r="Z42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA42">
         <v>9</v>
@@ -4294,25 +4294,25 @@
         <v>5</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W43">
         <v>5</v>
@@ -4383,25 +4383,25 @@
         <v>9</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W44">
         <v>10</v>
@@ -4419,7 +4419,7 @@
         <v>9</v>
       </c>
       <c r="AB44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC44">
         <v>9</v>
@@ -4472,25 +4472,25 @@
         <v>10</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W45">
         <v>10</v>
@@ -4766,7 +4766,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -4831,13 +4831,13 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U6">
         <v>100</v>
       </c>
       <c r="V6">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4899,13 +4899,13 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U7">
-        <v>93.5</v>
+        <v>93.8</v>
       </c>
       <c r="V7">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -5035,13 +5035,13 @@
         <v>100</v>
       </c>
       <c r="T9">
+        <v>93.8</v>
+      </c>
+      <c r="U9">
         <v>95.5</v>
       </c>
-      <c r="U9">
-        <v>97.40000000000001</v>
-      </c>
       <c r="V9">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -5307,13 +5307,13 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="V13">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -5511,13 +5511,13 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U16">
-        <v>90.90000000000001</v>
+        <v>92</v>
       </c>
       <c r="V16">
-        <v>95.5</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5647,13 +5647,13 @@
         <v>100</v>
       </c>
       <c r="T18">
+        <v>95.3</v>
+      </c>
+      <c r="U18">
         <v>95.5</v>
       </c>
-      <c r="U18">
-        <v>96.09999999999999</v>
-      </c>
       <c r="V18">
-        <v>95.5</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5715,13 +5715,13 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U19">
         <v>100</v>
       </c>
       <c r="V19">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5786,7 +5786,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>97.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -5919,13 +5919,13 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U22">
-        <v>92.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="V22">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5984,16 +5984,16 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>31.3</v>
+        <v>25</v>
       </c>
       <c r="T23">
-        <v>77.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U23">
-        <v>84.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="V23">
-        <v>84.8</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -6055,13 +6055,13 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U24">
         <v>100</v>
       </c>
       <c r="V24">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -6123,13 +6123,13 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U25">
         <v>100</v>
       </c>
       <c r="V25">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -6191,13 +6191,13 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="U26">
         <v>100</v>
       </c>
       <c r="V26">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6259,13 +6259,13 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U27">
-        <v>94.8</v>
+        <v>93.8</v>
       </c>
       <c r="V27">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6392,16 +6392,16 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>71.90000000000001</v>
+        <v>52.1</v>
       </c>
       <c r="T29">
-        <v>81.8</v>
+        <v>82.8</v>
       </c>
       <c r="U29">
-        <v>90.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="V29">
-        <v>86.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6460,16 +6460,16 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="T30">
-        <v>81.8</v>
+        <v>82.8</v>
       </c>
       <c r="U30">
-        <v>92.2</v>
+        <v>92</v>
       </c>
       <c r="V30">
-        <v>86.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6531,13 +6531,13 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U31">
         <v>100</v>
       </c>
       <c r="V31">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6599,13 +6599,13 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="U32">
         <v>100</v>
       </c>
       <c r="V32">
-        <v>93.90000000000001</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -6667,13 +6667,13 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U33">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="V33">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6735,13 +6735,13 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U34">
         <v>100</v>
       </c>
       <c r="V34">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -6803,13 +6803,13 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U35">
-        <v>94.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="V35">
-        <v>98.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -6927,25 +6927,25 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P37">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q37">
         <v>100</v>
       </c>
       <c r="R37">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S37">
-        <v>71.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="T37">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U37">
-        <v>90.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="V37">
-        <v>90.90000000000001</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -7075,13 +7075,13 @@
         <v>100</v>
       </c>
       <c r="T39">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U39">
-        <v>97.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="V39">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -7143,13 +7143,13 @@
         <v>100</v>
       </c>
       <c r="T40">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="U40">
-        <v>97.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="V40">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -7279,13 +7279,13 @@
         <v>100</v>
       </c>
       <c r="T42">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U42">
-        <v>97.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="V42">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -7347,13 +7347,13 @@
         <v>0</v>
       </c>
       <c r="T43">
-        <v>13.6</v>
+        <v>9.4</v>
       </c>
       <c r="U43">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="V43">
-        <v>9.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -7415,13 +7415,13 @@
         <v>100</v>
       </c>
       <c r="T44">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U44">
-        <v>97.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="V44">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -7555,16 +7555,16 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>88.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>11.9</v>
+        <v>7.1</v>
       </c>
       <c r="H2">
         <v>8</v>
@@ -7578,7 +7578,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
@@ -7599,7 +7599,7 @@
         <v>4.8</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7610,28 +7610,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4">
         <v>42</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7642,10 +7642,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>42</v>
@@ -7663,7 +7663,7 @@
         <v>2.4</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7674,10 +7674,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <v>42</v>
@@ -7695,7 +7695,7 @@
         <v>2.4</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7706,10 +7706,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7">
         <v>42</v>
@@ -7727,7 +7727,7 @@
         <v>2.4</v>
       </c>
       <c r="H7">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7738,10 +7738,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8">
         <v>42</v>
@@ -7759,7 +7759,7 @@
         <v>2.4</v>
       </c>
       <c r="H8">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7841,7 +7841,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920098</v>
+        <v>22330051920100</v>
       </c>
       <c r="B2" t="s">
         <v>77</v>
@@ -7899,10 +7899,10 @@
         <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4">
         <v>5</v>
